--- a/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,43 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font/>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,9 +76,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,7 +461,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="n">
+      <c r="A1" s="1" t="n">
         <v>2025</v>
       </c>
     </row>
@@ -431,67 +471,67 @@
           <t>INCOME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>SEPT</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>YR TOTAL</t>
         </is>
@@ -503,37 +543,37 @@
           <t>Business Income (Mercury rollup — includes art deals)</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>15000</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="3" t="n">
         <v>30000</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>14000</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>37200</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>41895</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>37034.79</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>10000</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="3" t="n">
         <v>22261.27</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>50670</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>6000</v>
       </c>
       <c r="M3" t="n">
@@ -550,40 +590,40 @@
           <t>Consultant</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="N4">
@@ -657,67 +697,67 @@
           <t>EXPENSES</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>FEB</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>MAR</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>APR</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>MAY</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>JUN</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>JUL</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>AUG</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>SEPT</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>NOV</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>DEC</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>YR TOTAL</t>
         </is>
@@ -729,43 +769,43 @@
           <t>Supplies (office and operating)</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
+      <c r="B8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -776,43 +816,43 @@
           <t>Office Construction</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
+      <c r="B9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -823,43 +863,43 @@
           <t>Office Interior</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
+      <c r="B10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -870,43 +910,43 @@
           <t>Office Furniture</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
+      <c r="B11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -917,43 +957,43 @@
           <t>Repairs and maintenance</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
+      <c r="B12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -964,43 +1004,43 @@
           <t>Advertising</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1" t="n">
+      <c r="B13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7" t="n">
         <v>755.98</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1" t="n">
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="G13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1">
+      <c r="G13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -1011,43 +1051,43 @@
           <t>Travel, Meals, and Entertainment</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
@@ -1058,43 +1098,43 @@
           <t>Accounting and legal</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="1">
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
@@ -1105,43 +1145,43 @@
           <t>Cellphone and Internet</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="7" t="n">
         <v>51.12</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="7" t="n">
         <v>93.26000000000001</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="7" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="7" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="7" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="7" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="7" t="n">
         <v>98.23</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="7" t="n">
         <v>98.34</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="7" t="n">
         <v>98.34</v>
       </c>
-      <c r="K16" s="1" t="n">
+      <c r="K16" s="7" t="n">
         <v>98.39</v>
       </c>
-      <c r="L16" s="1" t="n">
+      <c r="L16" s="7" t="n">
         <v>98.39</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="M16" s="7" t="n">
         <v>97.91</v>
       </c>
-      <c r="N16" s="1">
+      <c r="N16" s="5">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
@@ -1152,43 +1192,43 @@
           <t>Software Fees</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="7" t="n">
         <v>22.17</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="7" t="n">
         <v>22.17</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="7" t="n">
         <v>22.17</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="7" t="n">
         <v>22.17</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="7" t="n">
         <v>22.17</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="7" t="n">
         <v>22.17</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="7" t="n">
         <v>22.17</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="7" t="n">
         <v>2.17</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="7" t="n">
         <v>57.17</v>
       </c>
-      <c r="K17" s="1" t="n">
+      <c r="K17" s="7" t="n">
         <v>37.17</v>
       </c>
-      <c r="L17" s="1" t="n">
+      <c r="L17" s="7" t="n">
         <v>17.17</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="M17" s="7" t="n">
         <v>57.17</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="5">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
@@ -1199,43 +1239,43 @@
           <t>Tech</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1" t="n">
+      <c r="B18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="7" t="n">
         <v>192</v>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
+      <c r="G18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
@@ -1246,90 +1286,90 @@
           <t>Consultant Fees</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1">
+      <c r="B19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
         <f>SUM(B19:M19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Art Library</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="7" t="n">
         <v>153.44</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="7" t="n">
         <v>78.47</v>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="1" t="n">
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="n">
         <v>63.69</v>
       </c>
-      <c r="F20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1">
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
         <f>SUM(B20:M20)</f>
         <v/>
       </c>
@@ -1340,43 +1380,43 @@
           <t>Inventory / Art purchases (prefer Art Sales COGS — avoid double count)</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
+      <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
@@ -1405,7 +1445,7 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="3" t="n">
         <v>334.17</v>
       </c>
       <c r="I22" t="n">
@@ -1414,16 +1454,16 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22" s="3" t="n">
         <v>8658.629999999999</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22" s="3" t="n">
         <v>8000</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="3" t="n">
         <v>8146.75</v>
       </c>
-      <c r="N22" s="1">
+      <c r="N22" s="5">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
@@ -1434,43 +1474,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1">
+      <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5">
         <f>SUM(B23:M23)</f>
         <v/>
       </c>
@@ -1481,43 +1521,43 @@
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1">
+      <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5">
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
@@ -1528,55 +1568,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="5">
         <f>SUM(B8:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="5">
         <f>SUM(C8:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="5">
         <f>SUM(D8:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="5">
         <f>SUM(E8:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="5">
         <f>SUM(F8:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="5">
         <f>SUM(G8:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="5">
         <f>SUM(H8:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="5">
         <f>SUM(I8:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="5">
         <f>SUM(J8:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="1">
+      <c r="K25" s="5">
         <f>SUM(K8:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="1">
+      <c r="L25" s="5">
         <f>SUM(L8:L24)</f>
         <v/>
       </c>
-      <c r="M25" s="1">
+      <c r="M25" s="5">
         <f>SUM(M8:M24)</f>
         <v/>
       </c>
-      <c r="N25" s="1">
+      <c r="N25" s="5">
         <f>SUM(N8:N24)</f>
         <v/>
       </c>
@@ -1588,62 +1628,62 @@
           <t>YEAR TO DATE LESS EXPENSES</t>
         </is>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="5">
         <f>B5-B25</f>
         <v/>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="5">
         <f>C5-C25</f>
         <v/>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="5">
         <f>D5-D25</f>
         <v/>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="5">
         <f>E5-E25</f>
         <v/>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="5">
         <f>F5-F25</f>
         <v/>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="5">
         <f>G5-G25</f>
         <v/>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="5">
         <f>H5-H25</f>
         <v/>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="5">
         <f>I5-I25</f>
         <v/>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="5">
         <f>J5-J25</f>
         <v/>
       </c>
-      <c r="K27" s="1">
+      <c r="K27" s="5">
         <f>K5-K25</f>
         <v/>
       </c>
-      <c r="L27" s="1">
+      <c r="L27" s="5">
         <f>L5-L25</f>
         <v/>
       </c>
-      <c r="M27" s="1">
+      <c r="M27" s="5">
         <f>M5-M25</f>
         <v/>
       </c>
-      <c r="N27" s="1">
+      <c r="N27" s="5">
         <f>N5-N25</f>
         <v/>
       </c>
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>COGS for art objects = Cost column on Art Sales and Purchases tab (not this rollup).</t>
         </is>
@@ -1661,9 +1701,9 @@
     <row r="39"/>
     <row r="40"/>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CC starting point 2025-09-18: BoA 4469 ChatGPT/Google One/Tailor Brands/Abebooks/Blurb; Sapphire AT&amp;T cellphone (user) + Squarespace Tech + WW Norton; Prime Abebooks + Canva. Coinbase 6108: no EPGC operating charges (golf/museum/voids). TruGreen on BoA went to 524 Unit 2 yard, not EPGC. Yellow ASK on CC_LEDGER tab. Not tax advice.</t>
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>CC answers 2026-09-18: Canva CONFIRMED Software Fees; Park Chicago $100 + Field Museum $53 → Travel. Coinbase golf/voids still excluded; Soldier Field parking $57 HOLD. Frame Up / LAMA / Hindman are Art Sales inventory, not this P&amp;L. TruGreen is 524 yard. Not tax advice.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
@@ -81,10 +81,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -593,14 +593,14 @@
       <c r="B4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
+      <c r="C4" s="5" t="n">
+        <v>4100</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
+      <c r="E4" s="5" t="n">
+        <v>9200</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>0</v>
@@ -614,14 +614,14 @@
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
+      <c r="J4" s="5" t="n">
+        <v>4100</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="4" t="n">
-        <v>0</v>
+      <c r="L4" s="5" t="n">
+        <v>4100</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
@@ -769,43 +769,43 @@
           <t>Supplies (office and operating)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5">
+      <c r="B8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -816,43 +816,43 @@
           <t>Office Construction</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="5">
+      <c r="B9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -863,43 +863,43 @@
           <t>Office Interior</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5">
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -910,43 +910,43 @@
           <t>Office Furniture</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="5">
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -957,43 +957,43 @@
           <t>Repairs and maintenance</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5">
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -1004,43 +1004,43 @@
           <t>Advertising</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="n">
+      <c r="B13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>755.98</v>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="n">
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>199</v>
       </c>
-      <c r="G13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5">
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -1051,43 +1051,43 @@
           <t>Travel, Meals, and Entertainment</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="7" t="n">
+      <c r="B14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="7" t="n">
+      <c r="D14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="n">
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="7" t="n">
+      <c r="J14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="M14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="5">
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
@@ -1098,43 +1098,43 @@
           <t>Accounting and legal</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="5">
+      <c r="B15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="7">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
@@ -1145,43 +1145,43 @@
           <t>Cellphone and Internet</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="5" t="n">
         <v>51.12</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="5" t="n">
         <v>93.26000000000001</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="5" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="E16" s="7" t="n">
+      <c r="E16" s="5" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F16" s="5" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="5" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="5" t="n">
         <v>98.23</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="5" t="n">
         <v>98.34</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="J16" s="5" t="n">
         <v>98.34</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="K16" s="5" t="n">
         <v>98.39</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="5" t="n">
         <v>98.39</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="M16" s="5" t="n">
         <v>97.91</v>
       </c>
-      <c r="N16" s="5">
+      <c r="N16" s="7">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
@@ -1192,43 +1192,43 @@
           <t>Software Fees</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="5" t="n">
         <v>22.17</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>22.17</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="5" t="n">
         <v>22.17</v>
       </c>
-      <c r="E17" s="7" t="n">
+      <c r="E17" s="5" t="n">
         <v>22.17</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F17" s="5" t="n">
         <v>22.17</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="5" t="n">
         <v>22.17</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H17" s="5" t="n">
         <v>22.17</v>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="5" t="n">
         <v>2.17</v>
       </c>
-      <c r="J17" s="7" t="n">
+      <c r="J17" s="5" t="n">
         <v>57.17</v>
       </c>
-      <c r="K17" s="7" t="n">
+      <c r="K17" s="5" t="n">
         <v>37.17</v>
       </c>
-      <c r="L17" s="7" t="n">
+      <c r="L17" s="5" t="n">
         <v>17.17</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="M17" s="5" t="n">
         <v>57.17</v>
       </c>
-      <c r="N17" s="5">
+      <c r="N17" s="7">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
@@ -1239,43 +1239,43 @@
           <t>Tech</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7" t="n">
+      <c r="B18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F18" s="5" t="n">
         <v>192</v>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="5">
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="7">
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
@@ -1286,43 +1286,43 @@
           <t>Consultant Fees</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="5">
+      <c r="B19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="7">
         <f>SUM(B19:M19)</f>
         <v/>
       </c>
@@ -1333,43 +1333,43 @@
           <t>Art Library</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="5" t="n">
         <v>153.44</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="5" t="n">
         <v>78.47</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7" t="n">
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>63.69</v>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="5">
+      <c r="F20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="7">
         <f>SUM(B20:M20)</f>
         <v/>
       </c>
@@ -1380,43 +1380,43 @@
           <t>Inventory / Art purchases (prefer Art Sales COGS — avoid double count)</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="5">
+      <c r="B21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="7">
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
@@ -1463,7 +1463,7 @@
       <c r="M22" s="3" t="n">
         <v>8146.75</v>
       </c>
-      <c r="N22" s="5">
+      <c r="N22" s="7">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
@@ -1474,43 +1474,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="5">
+      <c r="B23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="7">
         <f>SUM(B23:M23)</f>
         <v/>
       </c>
@@ -1521,43 +1521,43 @@
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="5">
+      <c r="B24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="7">
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
@@ -1568,55 +1568,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="7">
         <f>SUM(B8:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="7">
         <f>SUM(C8:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="7">
         <f>SUM(D8:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="7">
         <f>SUM(E8:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="7">
         <f>SUM(F8:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="7">
         <f>SUM(G8:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="7">
         <f>SUM(H8:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="7">
         <f>SUM(I8:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="7">
         <f>SUM(J8:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="7">
         <f>SUM(K8:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="5">
+      <c r="L25" s="7">
         <f>SUM(L8:L24)</f>
         <v/>
       </c>
-      <c r="M25" s="5">
+      <c r="M25" s="7">
         <f>SUM(M8:M24)</f>
         <v/>
       </c>
-      <c r="N25" s="5">
+      <c r="N25" s="7">
         <f>SUM(N8:N24)</f>
         <v/>
       </c>
@@ -1628,62 +1628,62 @@
           <t>YEAR TO DATE LESS EXPENSES</t>
         </is>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="7">
         <f>B5-B25</f>
         <v/>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="7">
         <f>C5-C25</f>
         <v/>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="7">
         <f>D5-D25</f>
         <v/>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="7">
         <f>E5-E25</f>
         <v/>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="7">
         <f>F5-F25</f>
         <v/>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="7">
         <f>G5-G25</f>
         <v/>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="7">
         <f>H5-H25</f>
         <v/>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="7">
         <f>I5-I25</f>
         <v/>
       </c>
-      <c r="J27" s="5">
+      <c r="J27" s="7">
         <f>J5-J25</f>
         <v/>
       </c>
-      <c r="K27" s="5">
+      <c r="K27" s="7">
         <f>K5-K25</f>
         <v/>
       </c>
-      <c r="L27" s="5">
+      <c r="L27" s="7">
         <f>L5-L25</f>
         <v/>
       </c>
-      <c r="M27" s="5">
+      <c r="M27" s="7">
         <f>M5-M25</f>
         <v/>
       </c>
-      <c r="N27" s="5">
+      <c r="N27" s="7">
         <f>N5-N25</f>
         <v/>
       </c>
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>COGS for art objects = Cost column on Art Sales and Purchases tab (not this rollup).</t>
         </is>
@@ -1708,6 +1708,14 @@
       </c>
     </row>
     <row r="42"/>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Checking inflows 2026-09-18: GCM BOM PAYMEN $21500.00 → Consultant (ties 1099-NEC). JAKE C / SEFOF reimbursements $5214.69 EXCLUDED. ASK: EPGC LLC vs personal 1099. Bear Creek / UTMA not on this tab. Not tax advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
@@ -36,7 +36,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D5F5E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,17 +81,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -593,14 +602,14 @@
       <c r="B4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>4100</v>
+      <c r="C4" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>9200</v>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>0</v>
@@ -614,14 +623,14 @@
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>4100</v>
+      <c r="J4" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="5" t="n">
-        <v>4100</v>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="4" t="n">
         <v>0</v>
@@ -769,43 +778,43 @@
           <t>Supplies (office and operating)</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="7">
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6">
         <f>SUM(B8:M8)</f>
         <v/>
       </c>
@@ -816,43 +825,43 @@
           <t>Office Construction</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="7">
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6">
         <f>SUM(B9:M9)</f>
         <v/>
       </c>
@@ -863,43 +872,43 @@
           <t>Office Interior</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="7">
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6">
         <f>SUM(B10:M10)</f>
         <v/>
       </c>
@@ -910,43 +919,43 @@
           <t>Office Furniture</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="7">
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="6">
         <f>SUM(B11:M11)</f>
         <v/>
       </c>
@@ -957,43 +966,43 @@
           <t>Repairs and maintenance</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="7">
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6">
         <f>SUM(B12:M12)</f>
         <v/>
       </c>
@@ -1004,43 +1013,43 @@
           <t>Advertising</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="B13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8" t="n">
         <v>755.98</v>
       </c>
-      <c r="E13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <v>199</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="7">
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="6">
         <f>SUM(B13:M13)</f>
         <v/>
       </c>
@@ -1051,43 +1060,43 @@
           <t>Travel, Meals, and Entertainment</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="5" t="n">
+      <c r="B14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="5" t="n">
+      <c r="D14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5" t="n">
+      <c r="G14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="J14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="n">
+      <c r="J14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="L14" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="7">
+      <c r="M14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="6">
         <f>SUM(B14:M14)</f>
         <v/>
       </c>
@@ -1098,43 +1107,43 @@
           <t>Accounting and legal</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="7">
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="6">
         <f>SUM(B15:M15)</f>
         <v/>
       </c>
@@ -1145,43 +1154,43 @@
           <t>Cellphone and Internet</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="8" t="n">
         <v>51.12</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="8" t="n">
         <v>93.26000000000001</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="8" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="8" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="8" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="8" t="n">
         <v>98.26000000000001</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="8" t="n">
         <v>98.23</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I16" s="8" t="n">
         <v>98.34</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J16" s="8" t="n">
         <v>98.34</v>
       </c>
-      <c r="K16" s="5" t="n">
+      <c r="K16" s="8" t="n">
         <v>98.39</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="L16" s="8" t="n">
         <v>98.39</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="M16" s="8" t="n">
         <v>97.91</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="6">
         <f>SUM(B16:M16)</f>
         <v/>
       </c>
@@ -1192,43 +1201,43 @@
           <t>Software Fees</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="8" t="n">
         <v>22.17</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="8" t="n">
         <v>22.17</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="8" t="n">
         <v>22.17</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="8" t="n">
         <v>22.17</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="8" t="n">
         <v>22.17</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="8" t="n">
         <v>22.17</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" s="8" t="n">
         <v>22.17</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I17" s="8" t="n">
         <v>2.17</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J17" s="8" t="n">
         <v>57.17</v>
       </c>
-      <c r="K17" s="5" t="n">
+      <c r="K17" s="8" t="n">
         <v>37.17</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="L17" s="8" t="n">
         <v>17.17</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="M17" s="8" t="n">
         <v>57.17</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N17" s="6">
         <f>SUM(B17:M17)</f>
         <v/>
       </c>
@@ -1239,43 +1248,43 @@
           <t>Tech</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5" t="n">
+      <c r="B18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="8" t="n">
         <v>192</v>
       </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7">
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6">
         <f>SUM(B18:M18)</f>
         <v/>
       </c>
@@ -1286,90 +1295,90 @@
           <t>Consultant Fees</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="7">
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6">
         <f>SUM(B19:M19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Art Library</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="8" t="n">
         <v>153.44</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="8" t="n">
         <v>78.47</v>
       </c>
-      <c r="D20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5" t="n">
+      <c r="D20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="8" t="n">
         <v>63.69</v>
       </c>
-      <c r="F20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="7">
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6">
         <f>SUM(B20:M20)</f>
         <v/>
       </c>
@@ -1380,43 +1389,43 @@
           <t>Inventory / Art purchases (prefer Art Sales COGS — avoid double count)</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="7">
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="6">
         <f>SUM(B21:M21)</f>
         <v/>
       </c>
@@ -1463,7 +1472,7 @@
       <c r="M22" s="3" t="n">
         <v>8146.75</v>
       </c>
-      <c r="N22" s="7">
+      <c r="N22" s="6">
         <f>SUM(B22:M22)</f>
         <v/>
       </c>
@@ -1474,43 +1483,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="7">
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="6">
         <f>SUM(B23:M23)</f>
         <v/>
       </c>
@@ -1521,43 +1530,43 @@
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="7">
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="6">
         <f>SUM(B24:M24)</f>
         <v/>
       </c>
@@ -1568,55 +1577,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
         <f>SUM(B8:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="6">
         <f>SUM(C8:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <f>SUM(D8:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="6">
         <f>SUM(E8:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="6">
         <f>SUM(F8:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="6">
         <f>SUM(G8:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="6">
         <f>SUM(H8:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="7">
+      <c r="I25" s="6">
         <f>SUM(I8:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="7">
+      <c r="J25" s="6">
         <f>SUM(J8:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="7">
+      <c r="K25" s="6">
         <f>SUM(K8:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="7">
+      <c r="L25" s="6">
         <f>SUM(L8:L24)</f>
         <v/>
       </c>
-      <c r="M25" s="7">
+      <c r="M25" s="6">
         <f>SUM(M8:M24)</f>
         <v/>
       </c>
-      <c r="N25" s="7">
+      <c r="N25" s="6">
         <f>SUM(N8:N24)</f>
         <v/>
       </c>
@@ -1628,62 +1637,62 @@
           <t>YEAR TO DATE LESS EXPENSES</t>
         </is>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <f>B5-B25</f>
         <v/>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <f>C5-C25</f>
         <v/>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <f>D5-D25</f>
         <v/>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="6">
         <f>E5-E25</f>
         <v/>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <f>F5-F25</f>
         <v/>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="6">
         <f>G5-G25</f>
         <v/>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="6">
         <f>H5-H25</f>
         <v/>
       </c>
-      <c r="I27" s="7">
+      <c r="I27" s="6">
         <f>I5-I25</f>
         <v/>
       </c>
-      <c r="J27" s="7">
+      <c r="J27" s="6">
         <f>J5-J25</f>
         <v/>
       </c>
-      <c r="K27" s="7">
+      <c r="K27" s="6">
         <f>K5-K25</f>
         <v/>
       </c>
-      <c r="L27" s="7">
+      <c r="L27" s="6">
         <f>L5-L25</f>
         <v/>
       </c>
-      <c r="M27" s="7">
+      <c r="M27" s="6">
         <f>M5-M25</f>
         <v/>
       </c>
-      <c r="N27" s="7">
+      <c r="N27" s="6">
         <f>N5-N25</f>
         <v/>
       </c>
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>COGS for art objects = Cost column on Art Sales and Purchases tab (not this rollup).</t>
         </is>
@@ -1701,7 +1710,7 @@
     <row r="39"/>
     <row r="40"/>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>CC answers 2026-09-18: Canva CONFIRMED Software Fees; Park Chicago $100 + Field Museum $53 → Travel. Coinbase golf/voids still excluded; Soldier Field parking $57 HOLD. Frame Up / LAMA / Hindman are Art Sales inventory, not this P&amp;L. TruGreen is 524 yard. Not tax advice.</t>
         </is>
@@ -1709,9 +1718,9 @@
     </row>
     <row r="42"/>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Checking inflows 2026-09-18: GCM BOM PAYMEN $21500.00 → Consultant (ties 1099-NEC). JAKE C / SEFOF reimbursements $5214.69 EXCLUDED. ASK: EPGC LLC vs personal 1099. Bear Creek / UTMA not on this tab. Not tax advice.</t>
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Checking answers 2026-09-18: GCM BOM PAYMEN $21,500 REMOVED from EPGC Consultant (personal 1099 / GCM tab + Income E7 only). Consultant row is $0. JAKE C / SEFOF reimbursements $5214.69 still EXCLUDED. Bear Creek / UTMA not on this tab. Not tax advice.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
@@ -2311,8 +2311,8 @@
       <c r="F54" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="13" t="n">
-        <v>0</v>
+      <c r="G54" s="12" t="n">
+        <v>13595</v>
       </c>
       <c r="H54" s="13" t="n">
         <v>0</v>
@@ -3047,7 +3047,7 @@
     <row r="75">
       <c r="A75" s="17" t="inlineStr">
         <is>
-          <t>2025 Mercury unbundled 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Prior mixed Mercury dump removed. Consultant $0 until EOEB remainder $130,270.00 and L5 $87,396.32 are answered. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. 2024 leftover supplies/furniture/consultant-fee numbers on this 2025 block were zeroed. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. 2024 leftover supplies/furniture/consultant-fee numbers on this 2025 block were zeroed. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
@@ -2872,20 +2872,42 @@
           <t>Consultant Fees</t>
         </is>
       </c>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="6" t="n"/>
-      <c r="I69" s="6" t="n"/>
-      <c r="J69" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="6" t="n"/>
-      <c r="L69" s="6" t="n"/>
-      <c r="M69" s="6" t="n"/>
+      <c r="B69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>334.17</v>
+      </c>
+      <c r="I69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>658.63</v>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="N69" s="6">
         <f>SUM(B69:M69)</f>
         <v/>
@@ -3047,7 +3069,7 @@
     <row r="75">
       <c r="A75" s="17" t="inlineStr">
         <is>
-          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. 2024 leftover supplies/furniture/consultant-fee numbers on this 2025 block were zeroed. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
@@ -2253,7 +2253,7 @@
         <v>14000</v>
       </c>
       <c r="C53" s="12" t="n">
-        <v>135000</v>
+        <v>136000</v>
       </c>
       <c r="D53" s="13" t="n">
         <v>0</v>
@@ -3069,7 +3069,7 @@
     <row r="75">
       <c r="A75" s="17" t="inlineStr">
         <is>
-          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED cash only (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 Feb = $149,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED/LOCKED cash (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 / Aquinas books $1,000 Feb = $150,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. Aquinas books Cost TBD — cash on Art Sales, not in I8. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/EPGC LLC.xlsx
@@ -3069,7 +3069,7 @@
     <row r="75">
       <c r="A75" s="17" t="inlineStr">
         <is>
-          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED/LOCKED cash (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 / Aquinas books $1,000 Feb = $150,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 still ASK — not on Consultant income. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. Aquinas books Cost TBD — cash on Art Sales, not in I8. GCM 1099 is personal. Not tax advice.</t>
+          <t>2025 Mercury 2026-09-20: Art Sales = MATCHED/LOCKED cash (Berk $14,000 Jan + Berk $30,000 / mosaics $105,000 / Aquinas books $1,000 Feb = $150,000). Consultant June $13,595 = David Aaron Limited LOCKED (user: consultant fee, not a sale). Consultant Fees July $334.17 + October $658.63 = Wise expertise write-ups LOCKED ($992.80). EOEB remainder $130,270.00 and L5 $87,396.32 MIXED PATTERN CONFIRMED (art sales + advisory/consultant) — invoice-level split still ASK; not dumped onto Consultant or Art Sales. Koziol/Ariadne $150,000 LOCKED pass-through — not P&amp;L. Coinbase is Investments, not this tab. Newstar $23,581 is Art Sales COGS, not operating expense. Dec Wise $565.75 reimbursed — not on Consultant Fees. Aquinas books Cost TBD — cash on Art Sales, not in I8. GCM 1099 is personal. Not tax advice.</t>
         </is>
       </c>
     </row>
